--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF556FA-9D00-475C-A9A9-74768377C081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A36394-FAD0-47D7-ABB7-FC76A4663B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>乐加维林</t>
   </si>
@@ -158,10 +158,6 @@
   </si>
   <si>
     <t>小黑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小史莱姆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -696,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A15E30-5A88-440F-A215-A44746221EB5}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -774,27 +770,31 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -824,16 +824,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -842,7 +842,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>26</v>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -887,43 +887,43 @@
       <c r="A19" t="s">
         <v>34</v>
       </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
         <v>46</v>
       </c>
     </row>
@@ -931,12 +931,12 @@
       <c r="A26" t="s">
         <v>47</v>
       </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" t="s">
         <v>49</v>
       </c>
     </row>
@@ -952,23 +952,18 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
         <v>57</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A36394-FAD0-47D7-ABB7-FC76A4663B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE8B05B-5811-4C8F-BB79-D367D5C86ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -25,235 +25,248 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+  <si>
+    <t>倏忽魔</t>
+  </si>
+  <si>
+    <t>八体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜圈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>六火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卑鄙地精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胖地精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>愤怒地精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地精法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持盾地精</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地精头子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反冲机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖刺机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圆球守护者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哨卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圆球行者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地精大块头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奴隶头子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝奴隶贩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红奴隶贩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔内增生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大颚虫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄生鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虱虫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邪教徒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天罚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>守护者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小黑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖尖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗密欧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>壳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异蛇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打劫的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收藏家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火炬头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百夫长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘术士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弟勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心脏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被选者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觉醒者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铜人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圆球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾</t>
+  </si>
   <si>
     <t>乐加维林</t>
-  </si>
-  <si>
-    <t>倏忽魔</t>
-  </si>
-  <si>
-    <t>八体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甜圈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>六火</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛇刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛇女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卑鄙地精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胖地精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>愤怒地精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地精法师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持盾地精</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地精头子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反冲机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尖刺机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炸机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圆球守护者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哨卫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圆球行者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地精大块头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奴隶头子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝奴隶贩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红奴隶贩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>塔内增生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大颚虫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寄生鼠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虱虫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中史莱姆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邪教徒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小偷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天罚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>守护者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小黑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尖尖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗密欧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>熊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>巨口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>壳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异蛇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异鸟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打劫的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收藏家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火炬头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>百夫长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘术士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弟勇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>心脏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛇花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被选者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>觉醒者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铜人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圆球</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>矛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐加维林（睡）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>史老大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -286,7 +299,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,11 +318,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,283 +708,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A15E30-5A88-440F-A215-A44746221EB5}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>30</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
         <v>44</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
         <v>47</v>
-      </c>
-      <c r="B26" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
         <v>54</v>
-      </c>
-      <c r="B30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
         <v>56</v>
       </c>
-      <c r="B31" t="s">
-        <v>57</v>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE8B05B-5811-4C8F-BB79-D367D5C86ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C75E268-EE58-40C3-B605-748BCA07E5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -318,14 +318,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -708,23 +705,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A15E30-5A88-440F-A215-A44746221EB5}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -732,12 +729,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -745,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -765,7 +762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -782,22 +779,22 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -810,12 +807,8 @@
       <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -838,7 +831,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -848,44 +841,27 @@
       <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -922,63 +898,61 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A31" s="1" t="s">
         <v>59</v>
       </c>
     </row>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C75E268-EE58-40C3-B605-748BCA07E5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28776EF-8CE1-440A-9AEC-AB92E9957D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -705,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A15E30-5A88-440F-A215-A44746221EB5}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -893,66 +893,64 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
     </row>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28776EF-8CE1-440A-9AEC-AB92E9957D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBDA663-525D-4CAD-9248-E465205205ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -926,10 +926,10 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>42</v>
       </c>
     </row>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBDA663-525D-4CAD-9248-E465205205ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0444B225-4628-40B5-BE6A-691D601E4AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>倏忽魔</t>
   </si>
@@ -290,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,6 +300,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,11 +348,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -348,13 +396,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>126052</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,249 +757,247 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
+      <c r="A2" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B18" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0444B225-4628-40B5-BE6A-691D601E4AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C37F3D4-A0D4-4B3F-8203-C10B4B5F16C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -348,7 +348,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -368,9 +368,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -394,16 +391,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>126052</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>278452</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -433,7 +430,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5981700" y="466724"/>
+          <a:off x="5448300" y="200024"/>
           <a:ext cx="7860352" cy="5362575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -858,7 +855,6 @@
       <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -902,86 +898,86 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>0</v>
+      <c r="A16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C37F3D4-A0D4-4B3F-8203-C10B4B5F16C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA4E0E9-06EA-4EE0-B196-AA7DBB69FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -750,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A15E30-5A88-440F-A215-A44746221EB5}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -906,29 +906,32 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>0</v>
+      <c r="A17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -969,30 +972,25 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>56</v>
       </c>
     </row>

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA4E0E9-06EA-4EE0-B196-AA7DBB69FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CF208C-3982-4156-B5A1-78BA61703674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
+    <workbookView xWindow="5010" yWindow="2100" windowWidth="18375" windowHeight="12690" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -914,76 +914,76 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CF208C-3982-4156-B5A1-78BA61703674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D977408-D265-42FA-ACFF-B066CFEF3E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5010" yWindow="2100" windowWidth="18375" windowHeight="12690" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -936,44 +936,44 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>0</v>
+      <c r="A20" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">

--- a/doc/monster.xlsx
+++ b/doc/monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chaofan\AppData\Roaming\com.nesbox.tic\TIC-80\myproj\sts\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D977408-D265-42FA-ACFF-B066CFEF3E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5BDAA4-D195-408E-BD7B-9E272F84A098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5010" yWindow="2100" windowWidth="18375" windowHeight="12690" xr2:uid="{F23AF6A6-15E5-4CBC-A854-47F77E3852F2}"/>
   </bookViews>
@@ -290,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,24 +300,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,7 +330,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,15 +341,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -754,15 +727,15 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -782,7 +755,7 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -796,32 +769,32 @@
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -830,10 +803,10 @@
       <c r="D6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -841,157 +814,157 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
